--- a/Excel/6. Lookups/Lecture_5_Lookups.xlsx
+++ b/Excel/6. Lookups/Lecture_5_Lookups.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Advance_Excel_BI\6. Lookups\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DC_DDS_04\Excel\6. Lookups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454E3428-2E58-407A-855E-D52FBF728486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97095D3D-8CF1-4D58-AA81-20A3AEBA8CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="862" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="42">
   <si>
     <t>Example</t>
   </si>
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -334,7 +334,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,6 +356,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -499,7 +505,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -583,6 +589,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -613,33 +646,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -667,13 +673,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{07A69435-2566-40EA-825F-4AEE57686C93}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1555,24 +1564,24 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -1581,13 +1590,13 @@
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="44"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -1610,11 +1619,11 @@
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="47"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="56"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -1637,11 +1646,11 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="45"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="47"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="56"/>
       <c r="L6" s="22" t="s">
         <v>6</v>
       </c>
@@ -1660,11 +1669,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="45"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="47"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="56"/>
       <c r="L7" s="22" t="s">
         <v>7</v>
       </c>
@@ -1683,11 +1692,11 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="47"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="56"/>
       <c r="L8" s="22" t="s">
         <v>8</v>
       </c>
@@ -1706,11 +1715,11 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="47"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="56"/>
       <c r="L9" s="22" t="s">
         <v>9</v>
       </c>
@@ -1729,20 +1738,20 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="45"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="47"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="56"/>
       <c r="M10" s="21"/>
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="50"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="59"/>
       <c r="M11" s="21"/>
       <c r="O11" s="25"/>
     </row>
@@ -1762,13 +1771,13 @@
       <c r="N13" s="29"/>
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="53"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="43"/>
       <c r="L14" s="22" t="s">
         <v>16</v>
       </c>
@@ -1777,11 +1786,11 @@
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="54"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="56"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="46"/>
       <c r="L15" s="22" t="s">
         <v>6</v>
       </c>
@@ -1790,11 +1799,11 @@
       </c>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="54"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
       <c r="L16" s="22" t="s">
         <v>8</v>
       </c>
@@ -1804,11 +1813,11 @@
     </row>
     <row r="17" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
       <c r="L17" s="22" t="s">
         <v>14</v>
       </c>
@@ -1818,11 +1827,11 @@
     </row>
     <row r="18" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="56"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="46"/>
       <c r="L18" s="22" t="s">
         <v>15</v>
       </c>
@@ -1832,11 +1841,11 @@
     </row>
     <row r="19" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="6"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="56"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="46"/>
       <c r="L19" s="22" t="s">
         <v>7</v>
       </c>
@@ -1845,11 +1854,11 @@
       </c>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="54"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="56"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
       <c r="L20" s="22" t="s">
         <v>9</v>
       </c>
@@ -1858,11 +1867,11 @@
       </c>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="57"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="59"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
       <c r="L21" s="22" t="s">
         <v>5</v>
       </c>
@@ -1872,15 +1881,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="C4:G11"/>
     <mergeCell ref="C14:G21"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="K1:N1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:T1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="C4:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
@@ -1919,24 +1928,24 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -1945,13 +1954,13 @@
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="44"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -1960,11 +1969,11 @@
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="47"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="56"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -1983,11 +1992,11 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="45"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="47"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="56"/>
       <c r="L6" s="22" t="s">
         <v>5</v>
       </c>
@@ -2002,11 +2011,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="45"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="47"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="56"/>
       <c r="L7" s="22" t="s">
         <v>6</v>
       </c>
@@ -2021,11 +2030,11 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="47"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="56"/>
       <c r="L8" s="22" t="s">
         <v>7</v>
       </c>
@@ -2040,11 +2049,11 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="47"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="56"/>
       <c r="L9" s="22" t="s">
         <v>8</v>
       </c>
@@ -2059,11 +2068,11 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="45"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="47"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="56"/>
       <c r="L10" s="22" t="s">
         <v>9</v>
       </c>
@@ -2079,20 +2088,20 @@
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="50"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="59"/>
       <c r="L11" s="22" t="s">
         <v>16</v>
       </c>
       <c r="M11" s="23">
-        <f>HLOOKUP(M5,L15:S17,2,0)</f>
+        <f>HLOOKUP(M5,L15:S17,2,FALSE)</f>
         <v>83</v>
       </c>
       <c r="N11" s="23">
-        <f t="shared" ref="N11:O11" si="0">HLOOKUP(N5,M15:T17,2,0)</f>
+        <f t="shared" ref="N11:O11" si="0">HLOOKUP(N5,M15:T17,2,FALSE)</f>
         <v>99</v>
       </c>
       <c r="O11" s="23">
@@ -2116,22 +2125,22 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="53"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="43"/>
       <c r="M14" s="21"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="56"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="46"/>
       <c r="L15" s="20" t="s">
         <v>1</v>
       </c>
@@ -2159,11 +2168,11 @@
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
       <c r="L16" s="22" t="s">
         <v>16</v>
       </c>
@@ -2190,11 +2199,11 @@
       </c>
     </row>
     <row r="17" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="54"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
       <c r="L17" s="22" t="s">
         <v>17</v>
       </c>
@@ -2221,32 +2230,32 @@
       </c>
     </row>
     <row r="18" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="54"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="56"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="46"/>
     </row>
     <row r="19" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="54"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="56"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="46"/>
     </row>
     <row r="20" spans="3:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="54"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="56"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
     </row>
     <row r="21" spans="3:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="57"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="59"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2297,23 +2306,23 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="41"/>
+      <c r="L1" s="50"/>
       <c r="M1" s="15"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
       <c r="Z1" s="15"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2461,6 +2470,18 @@
       <c r="E10" s="64"/>
       <c r="F10" s="64"/>
       <c r="G10" s="65"/>
+      <c r="L10" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="22">
+        <v>95</v>
+      </c>
+      <c r="N10" s="22">
+        <v>99</v>
+      </c>
+      <c r="O10" s="22">
+        <v>99</v>
+      </c>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="63"/>
@@ -2479,7 +2500,7 @@
         <v>22</v>
       </c>
       <c r="M12" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N12" s="23"/>
     </row>
@@ -2493,11 +2514,11 @@
         <v>23</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N13" s="23">
         <f>IF(M13="Maths",1,IF(M13="Science",2,3))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2511,8 +2532,8 @@
         <v>21</v>
       </c>
       <c r="M14" s="23" cm="1">
-        <f t="array" ref="M14">INDEX(M5:O9,M12,N13)</f>
-        <v>30</v>
+        <f t="array" ref="M14">INDEX(M5:O10,M12,N13)</f>
+        <v>95</v>
       </c>
       <c r="N14" s="23"/>
     </row>
@@ -2525,64 +2546,64 @@
     </row>
     <row r="17" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5"/>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="53"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
     </row>
     <row r="18" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="56"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="46"/>
     </row>
     <row r="19" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="6"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="56"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="46"/>
     </row>
     <row r="20" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="54"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="56"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
     </row>
     <row r="21" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="54"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="56"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="46"/>
     </row>
     <row r="22" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="54"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="56"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="46"/>
     </row>
     <row r="23" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="54"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="56"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="46"/>
     </row>
     <row r="24" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="57"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="59"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2634,23 +2655,23 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
       <c r="O1" s="15"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
       <c r="Z1" s="15"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2711,7 +2732,7 @@
       <c r="L5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="22">
+      <c r="M5" s="69">
         <v>99</v>
       </c>
       <c r="N5" s="22">
@@ -2740,7 +2761,7 @@
       <c r="M6" s="22">
         <v>65</v>
       </c>
-      <c r="N6" s="22">
+      <c r="N6" s="69">
         <v>79</v>
       </c>
       <c r="O6" s="22">
@@ -2769,7 +2790,7 @@
       <c r="N7" s="22">
         <v>80</v>
       </c>
-      <c r="O7" s="22">
+      <c r="O7" s="69">
         <v>84</v>
       </c>
       <c r="P7" s="35">
@@ -2861,32 +2882,32 @@
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="53"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="43"/>
       <c r="L13" s="21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="56"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="46"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="56"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="46"/>
       <c r="L15" s="23"/>
       <c r="M15" s="20" t="s">
         <v>2</v>
@@ -2899,11 +2920,11 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="54"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
       <c r="L16" s="30" t="s">
         <v>26</v>
       </c>
@@ -2921,35 +2942,35 @@
       </c>
     </row>
     <row r="17" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="54"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
     </row>
     <row r="18" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="54"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="56"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="46"/>
       <c r="L18" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="54"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="56"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="46"/>
     </row>
     <row r="20" spans="3:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C20" s="57"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="59"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49"/>
       <c r="L20" s="23"/>
       <c r="M20" s="23" t="s">
         <v>28</v>
@@ -3032,23 +3053,23 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
       <c r="O1" s="15"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
       <c r="Z1" s="15"/>
     </row>
     <row r="2" spans="1:26" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -3230,13 +3251,13 @@
     </row>
     <row r="13" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="53"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="43"/>
       <c r="M13" s="28" t="s">
         <v>13</v>
       </c>
@@ -3246,11 +3267,11 @@
     </row>
     <row r="14" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="56"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="46"/>
       <c r="M14" s="24">
         <v>93</v>
       </c>
@@ -3260,11 +3281,11 @@
     </row>
     <row r="15" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="56"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="46"/>
       <c r="M15" s="24">
         <v>62</v>
       </c>
@@ -3273,11 +3294,11 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C16" s="54"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
       <c r="M16" s="24">
         <v>82</v>
       </c>
@@ -3286,11 +3307,11 @@
       </c>
     </row>
     <row r="17" spans="3:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C17" s="54"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
       <c r="M17" s="24">
         <v>99</v>
       </c>
@@ -3299,11 +3320,11 @@
       </c>
     </row>
     <row r="18" spans="3:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C18" s="54"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="56"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="46"/>
       <c r="M18" s="24">
         <v>65</v>
       </c>
@@ -3312,11 +3333,11 @@
       </c>
     </row>
     <row r="19" spans="3:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C19" s="54"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="56"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="46"/>
       <c r="M19" s="24">
         <v>85</v>
       </c>
@@ -3325,11 +3346,11 @@
       </c>
     </row>
     <row r="20" spans="3:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C20" s="57"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="59"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49"/>
       <c r="M20" s="24">
         <v>100</v>
       </c>
@@ -3371,15 +3392,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="15"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
